--- a/data/03_03_2025.xlsx
+++ b/data/03_03_2025.xlsx
@@ -438,9 +438,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>45719</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="B2" s="4">
         <v>5.2777777777777778E-2</v>
       </c>
